--- a/tools/importer/reports/import-homepage.report.xlsx
+++ b/tools/importer/reports/import-homepage.report.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="16">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="56" uniqueCount="49">
   <si>
     <t>_reportFile</t>
   </si>
@@ -37,6 +37,48 @@
     <t>url</t>
   </si>
   <si>
+    <t>contact.report.json</t>
+  </si>
+  <si>
+    <t>["#main &gt; header.banner","#main &gt; article &gt; section:nth-of-type(1) .l-columns","#main &gt; article &gt; section:nth-of-type(1) .l-columns","#main &gt; article &gt; section:nth-of-type(3) .l-columns","#main &gt; article &gt; section:nth-of-type(4) .l-columns","#main &gt; article &gt; section:nth-of-type(4) .l-columns","#main &gt; article &gt; section:nth-of-type(5) .l-columns","#main &gt; article &gt; section:nth-of-type(5) .l-columns"]</t>
+  </si>
+  <si>
+    <t>contact</t>
+  </si>
+  <si>
+    <t>success</t>
+  </si>
+  <si>
+    <t>2026-08-22T23:54:48.145Z</t>
+  </si>
+  <si>
+    <t>Contact Us | Fluence - A Siemens and AES Company</t>
+  </si>
+  <si>
+    <t>https://fluenceenergy.com/contact/</t>
+  </si>
+  <si>
+    <t>energy-storage-services.report.json</t>
+  </si>
+  <si>
+    <t>["#main &gt; header.banner","#main &gt; article &gt; section:nth-of-type(3) .l-columns--2","#main &gt; article &gt; section:nth-of-type(5) .l-columns--2","#main &gt; article &gt; section:nth-of-type(6) .l-columns--2","#main &gt; article &gt; section:nth-of-type(7) .l-columns--2","#main &gt; article &gt; section:nth-of-type(9) .l-columns--2","#main &gt; article &gt; section:nth-of-type(4) .l-columns--3","#main &gt; article &gt; section:nth-of-type(8) .l-columns--4","#main &gt; article &gt; section:nth-of-type(11) .l-grid"]</t>
+  </si>
+  <si>
+    <t>energy-storage-services</t>
+  </si>
+  <si>
+    <t>services</t>
+  </si>
+  <si>
+    <t>2026-08-22T23:54:26.425Z</t>
+  </si>
+  <si>
+    <t>Energy Storage Services | Fluence - A Siemens and AES Company</t>
+  </si>
+  <si>
+    <t>https://fluenceenergy.com/energy-storage-services/</t>
+  </si>
+  <si>
     <t>index.report.json</t>
   </si>
   <si>
@@ -46,19 +88,76 @@
     <t>index</t>
   </si>
   <si>
-    <t>success</t>
-  </si>
-  <si>
     <t>homepage</t>
   </si>
   <si>
-    <t>2026-08-21T21:16:26.351Z</t>
+    <t>2026-08-24T16:22:59.345Z</t>
   </si>
   <si>
     <t>Fluence | A Siemens and AES Company</t>
   </si>
   <si>
     <t>https://fluenceenergy.com/</t>
+  </si>
+  <si>
+    <t>mosaic-intelligent-bidding-software.report.json</t>
+  </si>
+  <si>
+    <t>["#main &gt; header.banner","#main &gt; .banner-nav-animation-wrap nav.navigation--banner","#main article &gt; section:nth-of-type(1) .columns-two-thirds","#main article &gt; section:nth-of-type(5) .columns-two-thirds","#main article &gt; section:nth-of-type(2) blockquote","#main article &gt; section:nth-of-type(7) .l-columns--3","#main article &gt; section:nth-of-type(7) .l-columns--3","#main article &gt; section:nth-of-type(3)","#main article &gt; section:nth-of-type(9) .l-columns--3","#main article &gt; section:nth-of-type(9) .l-columns--3","#main article &gt; section:nth-of-type(10) .l-columns--3","#main article &gt; section:nth-of-type(12) .l-grid--four-col"]</t>
+  </si>
+  <si>
+    <t>mosaic-intelligent-bidding-software</t>
+  </si>
+  <si>
+    <t>mosaic</t>
+  </si>
+  <si>
+    <t>2026-08-23T01:30:25.793Z</t>
+  </si>
+  <si>
+    <t>Bidding Software for Wind, Solar, and Energy Storage</t>
+  </si>
+  <si>
+    <t>https://fluenceenergy.com/mosaic-intelligent-bidding-software/</t>
+  </si>
+  <si>
+    <t>nispera-energy-asset-performance-management-software.report.json</t>
+  </si>
+  <si>
+    <t>["#main &gt; header.banner","#main &gt; article &gt; section:nth-of-type(1) .columns-two-thirds","#main &gt; article &gt; section:nth-of-type(4) .l-columns--2","#main &gt; article &gt; section:nth-of-type(5).split-content-section","#main &gt; article &gt; section:nth-of-type(6) .l-columns--2","#main &gt; article &gt; section:nth-of-type(8).split-content-section","#main &gt; article &gt; section:nth-of-type(11) .l-columns--2","#main &gt; article &gt; section:nth-of-type(12).split-content-section","#main &gt; article &gt; section:nth-of-type(14).split-content-section","#main &gt; article &gt; section:nth-of-type(3) blockquote","#main &gt; article &gt; section:nth-of-type(10) blockquote","#main &gt; article &gt; section:nth-of-type(2) .l-columns--4","#main &gt; article &gt; section:nth-of-type(16) .l-grid"]</t>
+  </si>
+  <si>
+    <t>nispera-energy-asset-performance-management-software</t>
+  </si>
+  <si>
+    <t>nispera</t>
+  </si>
+  <si>
+    <t>2026-08-22T23:54:37.618Z</t>
+  </si>
+  <si>
+    <t>Asset Performance Management Software for Wind, Solar, Energy Storage</t>
+  </si>
+  <si>
+    <t>https://fluenceenergy.com/nispera-energy-asset-performance-management-software/</t>
+  </si>
+  <si>
+    <t>sustainability.report.json</t>
+  </si>
+  <si>
+    <t>["#main &gt; header.banner","#main &gt; article &gt; section:nth-of-type(2).split-content-section","#main &gt; article &gt; section:nth-of-type(3) .l-columns--2","#main &gt; article &gt; section:nth-of-type(5) .l-columns--2","#main &gt; article &gt; section:nth-of-type(8) .l-columns--2","#main &gt; article &gt; section:nth-of-type(11) .l-columns--2","#main &gt; article &gt; section:nth-of-type(14) .l-columns--2","#main &gt; article &gt; section:nth-of-type(6) .l-columns--3","#main &gt; article &gt; section:nth-of-type(6) .l-columns--4","#main &gt; article &gt; section:nth-of-type(18) .l-columns--3"]</t>
+  </si>
+  <si>
+    <t>sustainability</t>
+  </si>
+  <si>
+    <t>2026-08-22T22:10:49.130Z</t>
+  </si>
+  <si>
+    <t>Sustainability | Fluence</t>
+  </si>
+  <si>
+    <t>https://fluenceenergy.com/sustainability/</t>
   </si>
 </sst>
 </file>
@@ -447,16 +546,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:H2"/>
+  <dimension ref="A1:H7"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
-    <col min="1" max="1" width="19" customWidth="1"/>
-    <col min="2" max="2" width="50" customWidth="1"/>
-    <col min="3" max="3" width="7" customWidth="1"/>
-    <col min="5" max="5" width="10" customWidth="1"/>
+    <col min="1" max="3" width="50" customWidth="1"/>
+    <col min="5" max="5" width="16" customWidth="1"/>
     <col min="6" max="6" width="26" customWidth="1"/>
-    <col min="7" max="7" width="37" customWidth="1"/>
-    <col min="8" max="8" width="28" customWidth="1"/>
+    <col min="7" max="8" width="50" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:8" s="1" customFormat="1" x14ac:dyDescent="0.25">
@@ -499,16 +595,146 @@
         <v>11</v>
       </c>
       <c r="E2" t="s">
+        <v>10</v>
+      </c>
+      <c r="F2" t="s">
         <v>12</v>
       </c>
-      <c r="F2" t="s">
+      <c r="G2" t="s">
         <v>13</v>
       </c>
-      <c r="G2" t="s">
+      <c r="H2" t="s">
         <v>14</v>
       </c>
-      <c r="H2" t="s">
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
         <v>15</v>
+      </c>
+      <c r="B3" t="s">
+        <v>16</v>
+      </c>
+      <c r="C3" t="s">
+        <v>17</v>
+      </c>
+      <c r="D3" t="s">
+        <v>11</v>
+      </c>
+      <c r="E3" t="s">
+        <v>18</v>
+      </c>
+      <c r="F3" t="s">
+        <v>19</v>
+      </c>
+      <c r="G3" t="s">
+        <v>20</v>
+      </c>
+      <c r="H3" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>22</v>
+      </c>
+      <c r="B4" t="s">
+        <v>23</v>
+      </c>
+      <c r="C4" t="s">
+        <v>24</v>
+      </c>
+      <c r="D4" t="s">
+        <v>11</v>
+      </c>
+      <c r="E4" t="s">
+        <v>25</v>
+      </c>
+      <c r="F4" t="s">
+        <v>26</v>
+      </c>
+      <c r="G4" t="s">
+        <v>27</v>
+      </c>
+      <c r="H4" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>29</v>
+      </c>
+      <c r="B5" t="s">
+        <v>30</v>
+      </c>
+      <c r="C5" t="s">
+        <v>31</v>
+      </c>
+      <c r="D5" t="s">
+        <v>11</v>
+      </c>
+      <c r="E5" t="s">
+        <v>32</v>
+      </c>
+      <c r="F5" t="s">
+        <v>33</v>
+      </c>
+      <c r="G5" t="s">
+        <v>34</v>
+      </c>
+      <c r="H5" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>36</v>
+      </c>
+      <c r="B6" t="s">
+        <v>37</v>
+      </c>
+      <c r="C6" t="s">
+        <v>38</v>
+      </c>
+      <c r="D6" t="s">
+        <v>11</v>
+      </c>
+      <c r="E6" t="s">
+        <v>39</v>
+      </c>
+      <c r="F6" t="s">
+        <v>40</v>
+      </c>
+      <c r="G6" t="s">
+        <v>41</v>
+      </c>
+      <c r="H6" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>43</v>
+      </c>
+      <c r="B7" t="s">
+        <v>44</v>
+      </c>
+      <c r="C7" t="s">
+        <v>45</v>
+      </c>
+      <c r="D7" t="s">
+        <v>11</v>
+      </c>
+      <c r="E7" t="s">
+        <v>45</v>
+      </c>
+      <c r="F7" t="s">
+        <v>46</v>
+      </c>
+      <c r="G7" t="s">
+        <v>47</v>
+      </c>
+      <c r="H7" t="s">
+        <v>48</v>
       </c>
     </row>
   </sheetData>
